--- a/www/download/COUNTRY.CHE.EXI382.xlsx
+++ b/www/download/COUNTRY.CHE.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Suíça</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10720306748466</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10720306748466</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10720306748466</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.10718711656442</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.371</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.675</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3.272</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3.639</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3.677</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3.302</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3.475</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3.464</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>3.938</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3.459</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3.467</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>3.528</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3.414</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.031</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.172</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4.239</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>4.265</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4.101</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>4.528</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>4.517</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>4.332</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>4.185</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>4.428</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4.311</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.609</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.059</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2.714</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.016</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3.066</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.743</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.733</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.895</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.891</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.281</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.911</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.929</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.982</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.456</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.918</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.474</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3.033</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3.589</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3.641</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>3.644</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>3.489</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3.842</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>3.821</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>3.653</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>3.517</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>3.705</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3.598</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>8461.804</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>7119.702</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>6442.48</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>7080.755</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>7146.634</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>6600.072</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6613.249</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>6974.77</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>6825.583</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>7692.919</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>6926.7</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>6948.99</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>7086.695</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>7973.343</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>6846.695</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>7817.464</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>7042.354</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8100.009</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>8186.731</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>8228.331</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>7895.484</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8702.257</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>8681.695</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>8363.094</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>8070.183</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>8544.563</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>8302.296</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6877.29</t>
+          <t>26437501123.645</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4443.88</t>
+          <t>15352748294.3924</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3897.107</t>
+          <t>14825633052.2401</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4391.743</t>
+          <t>16267979280.1487</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4486.604</t>
+          <t>15951085973.3506</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3948.424</t>
+          <t>15541376762.8747</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3916.299</t>
+          <t>15518641957.2214</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4250.937</t>
+          <t>15994739735.2648</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4160.643</t>
+          <t>15481832578.7578</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4844.361</t>
+          <t>18726274042.1993</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4366.134</t>
+          <t>18588099730.3291</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4398.988</t>
+          <t>19033345993.565</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4548.187</t>
+          <t>16108708918.1553</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5310.759</t>
+          <t>20999288107.7856</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4509.974</t>
+          <t>19699698771.0882</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5388.134</t>
+          <t>18144984698.4152</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>4662.976</t>
+          <t>20299537494.525</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5605.617</t>
+          <t>20857424278.8792</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5657.323</t>
+          <t>22214367312.1522</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>6911.529</t>
+          <t>18972411346.5173</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>6598.581</t>
+          <t>19215639856.5063</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7256.344</t>
+          <t>20365124236.219</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>7217.555</t>
+          <t>18355943773.2275</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6936.542</t>
+          <t>19864413950.8574</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>6669.713</t>
+          <t>17867610822.1893</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>7032.485</t>
+          <t>21029462162.4732</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6819.905</t>
+          <t>25392349348.9408</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7868275310.78325</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4705778817.50113</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4695197339.30645</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5166484420.87591</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4601019516.99788</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4940566250.37072</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5075163208.38084</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4884004517.9171</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4638237230.22807</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5608603602.38757</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5744446190.52636</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5226443233.4005</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4541359377.06309</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>5411530222.95916</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5311794528.13955</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>6292812844.91196</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5617921808.50423</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>7581969774.48969</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>8745334639.16088</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>5856538518.9288</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>5942666609.60904</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6826982392.3056</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>6453545928.34041</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5577094655.70763</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>5850153648.40299</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>5151623623.62491</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>6789786401.86492</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8728185.67727595</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5678480.47395134</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5427958.46123227</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5904396.93967008</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5631572.07050566</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5619207.79295886</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5689240.604429</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5744886.01409631</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5472343.93755942</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5788527.16164776</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5178577.64777137</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4993529.81949</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4944035.91690747</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5463768.00197719</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4571651.7654436</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3607989.42192166</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3542209.09384045</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3474120.95475605</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>3647566.34529426</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>31596168691609.4</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2777635.41362391</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2880498.24729895</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2829129.24724367</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3265496.17569477</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2703958.03639771</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2882393.772792</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3488176.28531473</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14796.4094211837</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>29437.6272937021</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>26672.0418663627</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>32593.4773303903</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>34226.3880434959</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>34674.3051589144</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35543.6957217698</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>35984.7752113634</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>31531.0291549341</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>37999.7015742984</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>32657.8579755632</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>35612.0027765838</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>37639.3485314292</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>47887.7521633835</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>36656.1343977328</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>53779.8773413248</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>43907.9595829005</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>62785.7079511003</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>61394.0521788496</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>59756.3286163351</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>66576.7901601073</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>63896.6968315118</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>67867.6517751313</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>62744.0056066995</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>63621.6680754817</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>62467.866909189</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>63102.6451318574</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>98548.4990241234</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>116666.646282927</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>122706.190614831</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>138423.276223697</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>143165.699732649</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>166740.532348138</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>167178.473143987</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>167027.256320981</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>148513.837941159</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>175547.991398322</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>186806.16005038</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>204614.367891379</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>179417.384769188</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>235013.732953696</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>220935.058985151</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>234675.614508356</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>273319.281298694</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>309969.463861483</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>322485.509296433</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>285083.984224829</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>326169.098292514</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>315077.752307791</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>300249.836245428</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>316012.129401812</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>302853.693803766</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>339088.658777609</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>401977.653236952</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.125946893604415</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.0556547231940007</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.169980148145213</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.149955241855313</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.0248674270073402</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.200815493627875</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.228340284006227</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.129620584009673</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.102968909635677</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.136262545290183</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.239938219423274</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.158320907058326</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.00150343154314969</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.0186215763022449</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.150950968433156</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.143763825050552</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.169982039810294</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.260664818414224</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.353103885279886</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.180138975569439</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.110373746066645</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.0628918012199413</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.118386010281642</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.243755532807918</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.140091871168241</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.365100615299589</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.00443589854374005</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2180.05249096907</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1538.18808796204</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1729.8004418482</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1712.96854244765</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1500.56079740363</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1801.02298424111</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1857.21434432683</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1687.01905594653</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1604.52385828055</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1709.41895836318</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1973.22279147011</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1784.4998748294</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1522.92400303892</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1565.70037987441</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1820.66650493197</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1811.50695057657</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1852.14354757509</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2112.67548330604</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2401.97056748575</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1607.11561030251</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1703.03994564679</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1776.96807677235</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1689.15099366989</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1526.83462719445</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1663.22686504274</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1390.33369451797</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1886.84101220448</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>21173659649.941</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>8602272341.57432</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>8729515886.24916</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>8862593271.62739</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>9143993106.90586</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>10147008645.2631</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>10105443640.0587</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>10835288476.2659</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>10322084241.0835</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>13443863282.4225</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>12994181127.0771</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>13114276815.4671</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>11874140256.8941</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>14504824461.1965</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>13338197469.1178</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>15830107222.9726</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>16284183111.8335</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>17502815799.6063</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>19622206997.566</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>16653427525.2636</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>17130963632.133</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>19231470805.5173</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>15075309021.227</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>16827083644.8374</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>16218283965.8554</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>17353028789.786</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>19357825341.8607</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16388456843.6718</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6395327131.34509</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6305198111.93104</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6402957506.80234</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6716948323.22563</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>7930149115.10273</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8242665518.67113</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>8793224757.23662</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>8446951732.33898</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>11046731559.0789</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>9853731509.79507</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>10061042118.6892</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>8536394548.22658</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10492125309.8017</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>9810638549.71812</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>10851860547.0434</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>11757000167.4229</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>12054043342.657</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>13386278102.6616</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>11782122841.6021</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>11515021275.3116</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>13060855539.9535</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>13394956954.9199</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14904181791.8755</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>14584013268.1543</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15698910535.1673</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>15437461022.8799</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4785202806.26919</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2206945210.22923</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2424317774.31812</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2459635764.82505</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2427044783.68024</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2216859530.16037</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1862778121.38756</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2042063719.0293</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1875132508.74447</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2397131723.34355</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3140449617.28202</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3053234696.77792</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>3337745708.66753</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>4012699151.39478</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>3527558919.3997</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>4978246675.92923</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4527182944.4106</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>5448772456.94927</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>6235928894.90444</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>4871304683.66152</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>5615942356.82144</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>6170615265.56375</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1680352066.3071</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>1922901852.96194</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1634270697.70106</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1654118254.6187</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3920364318.98086</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>1905.48165183695</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1452.5806557062</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>1435.76870648119</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>1456.09993037437</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>1463.24571130412</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>1439.34966462559</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>1433.1374934828</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>1468.34666067929</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>1439.30778610897</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>1476.48918012932</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>1499.77122835935</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>1501.97623600094</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>1525.21361502291</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>1536.54457078413</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>1545.83513281868</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>1551.07778225602</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1537.3124093368</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1561.97531208189</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1553.8254277786</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>1896.61976996405</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1891.01084414896</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1888.72479983089</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1889.12284057374</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1899.00901525581</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1896.23142874387</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1897.94538185823</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1895.21084750279</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>1935.72717024668</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>1937.28116241836</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>1968.73242879952</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1945.85039435065</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>1943.6574288125</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>1994.03969908472</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>2002.55844234564</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>2007.07030013505</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>1970.32013163206</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1953.65797292942</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>2002.74677615264</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>2004.49707214374</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2008.8142751851</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>1954.44234728923</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>2005.41724026788</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1939.43237074546</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>1983.53819288017</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>1941.65663878024</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>1931.28827553649</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>1929.11627390895</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>1925.32485043985</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1922.04244730769</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>1921.94236298216</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>1930.6472969391</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>1928.48252472138</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>1929.52683551996</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>1926.02861640918</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>104549.797426097</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>106308.144597237</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>121360.704981948</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>123893.963769633</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>130848.093319478</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>157073.029398364</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>161575.880645621</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>156964.663118291</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>141081.266542848</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>152037.572019626</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>163799.290710248</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>174358.71487483</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>184092.080355487</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>199744.206024954</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>198307.431837478</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>267607.337482836</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>311395.968250625</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>332714.518270514</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>356857.204160109</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>313380.344110798</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>375634.210487166</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>397407.396202397</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>377110.453570594</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>377677.845974852</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>401245.59885446</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>423410.674505746</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>446322.531966017</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6450085453.42809</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3231111412.52809</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3446540586.86021</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>3741056429.56243</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3716019231.13077</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4426115576.49771</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4233262765.67965</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3989575625.96523</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>3763037806.40149</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>4156411499.85917</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3945661986.52102</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>4231171563.32862</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3773142565.68257</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>4694888425.85937</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>4731560070.56292</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>4672595482.24894</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>5519988928.3604</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>5503447473.46945</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6316137453.395</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>5116639135.51426</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>5125957826.45183</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>5884179151.36114</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>5872018584.16187</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>6818142614.14541</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>5810865349.63423</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>7839381227.62548</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>7939700856.58851</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>90505.8413913487</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>94008.8289722828</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>105058.146116324</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>109347.436311542</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>115445.402725907</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>135428.191453336</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>140710.273091545</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>130774.124715342</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>116022.388342789</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>117076.775948656</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>134384.443921055</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>136904.202372513</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>132567.574563043</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>146003.809541974</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>158952.131742509</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>202630.329982975</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>252340.614662368</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>257020.518534955</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>273524.299643904</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>231466.983920406</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>279022.723985568</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>301900.154902686</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>288288.268556332</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>275561.187778562</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>296117.186637212</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>314672.762820342</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>332511.488701648</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8461.804</t>
+          <t>19667475500.5135</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7119.702</t>
+          <t>9334924776.266</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6442.48</t>
+          <t>9124417694.7526</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7080.755</t>
+          <t>9863108358.59281</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7146.634</t>
+          <t>10034482815.0912</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6600.072</t>
+          <t>11215131544.0067</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6613.249</t>
+          <t>10973522323.766</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6974.77</t>
+          <t>10442308315.2622</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6825.583</t>
+          <t>9828178529.46753</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7692.919</t>
+          <t>11188819926.8797</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6926.7</t>
+          <t>12020192800.5187</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6948.99</t>
+          <t>11772527806.1077</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>7086.695</t>
+          <t>9248845827.42897</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>7973.343</t>
+          <t>11835163913.996</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6846.695</t>
+          <t>12276995428.3448</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>7817.464</t>
+          <t>12490906661.8417</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>7042.354</t>
+          <t>14994159336.2432</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8100.009</t>
+          <t>14753253261.3445</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8186.731</t>
+          <t>16392263839.4825</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>8228.331</t>
+          <t>13062177411.9883</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>7895.484</t>
+          <t>12917983380.593</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>8702.257</t>
+          <t>14986483188.4787</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>8681.695</t>
+          <t>12391729860.0025</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>8363.094</t>
+          <t>13495881607.3332</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>8070.183</t>
+          <t>12434351825.2649</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>8544.563</t>
+          <t>14640338834.5401</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>8302.296</t>
+          <t>16208338777.5704</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6877.29</t>
+          <t>14043.9560347486</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4443.88</t>
+          <t>12299.3156249537</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3897.107</t>
+          <t>16302.5588656241</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4391.743</t>
+          <t>14546.5274580909</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4486.604</t>
+          <t>15402.6905935715</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3948.424</t>
+          <t>21644.837945028</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3916.299</t>
+          <t>20865.6075540753</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4250.937</t>
+          <t>26190.5384029499</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4160.643</t>
+          <t>25058.8782000593</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4844.361</t>
+          <t>34960.7960709698</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4366.134</t>
+          <t>29414.8467891937</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4398.988</t>
+          <t>37454.5125023163</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4548.187</t>
+          <t>51524.5057924442</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5310.759</t>
+          <t>53740.3964829802</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4509.974</t>
+          <t>39355.3000949688</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>5388.134</t>
+          <t>64977.0074998609</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>4662.976</t>
+          <t>59055.3535882577</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5605.617</t>
+          <t>75693.9997355586</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5657.323</t>
+          <t>83332.9045162053</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>6911.529</t>
+          <t>81913.3601903923</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>6598.581</t>
+          <t>96611.4865015972</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>7256.344</t>
+          <t>95507.2412997109</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>7217.555</t>
+          <t>88822.1850142625</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6936.542</t>
+          <t>102116.65819629</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>6669.713</t>
+          <t>105128.412217247</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>7032.485</t>
+          <t>108737.911685404</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>6819.905</t>
+          <t>113811.04326437</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17317.823</t>
+          <t>-13217390047.0854</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10603.718</t>
+          <t>-6103813363.73791</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10173.75</t>
+          <t>-5677877107.89239</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11181.603</t>
+          <t>-6122051929.03038</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10965.694</t>
+          <t>-6318463583.96042</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>10578.832</t>
+          <t>-6789015967.50896</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10544.83</t>
+          <t>-6740259558.08634</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10879.516</t>
+          <t>-6452732689.29694</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>10527.073</t>
+          <t>-6065140723.06603</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12710.091</t>
+          <t>-7032408427.02049</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>12411.637</t>
+          <t>-8074530813.99771</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>12727.575</t>
+          <t>-7541356242.77907</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10930.606</t>
+          <t>-5475703261.7464</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>14155.797</t>
+          <t>-7140275488.13666</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>13090.193</t>
+          <t>-7545435357.78185</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>12325.225</t>
+          <t>-7818311179.59273</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>13285.079</t>
+          <t>-9474170407.88275</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>13955.699</t>
+          <t>-9249805787.87507</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>14995.535</t>
+          <t>-10076126386.0875</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>12806.273</t>
+          <t>-7945538276.47401</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>12814.197</t>
+          <t>-7792025554.14121</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>13624.466</t>
+          <t>-9102304037.11759</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>12520.719</t>
+          <t>-6519711275.84068</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13217.529</t>
+          <t>-6677738993.18779</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>11962.072</t>
+          <t>-6623486475.63068</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13952.576</t>
+          <t>-6800957606.91462</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>16046.454</t>
+          <t>-8268637920.98184</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>92665.1000311664</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>83462.1944436273</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>93777.5092920197</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>96212.1979526654</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84685.0870053813</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>91273.7957911423</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>96900.7912619907</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>101423.376818681</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>112937.714730747</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>99797.4622341992</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>102613.296144639</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>107875.398385805</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>127120.721226733</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>117302.507787161</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>140267.559760885</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>135236.487289244</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>157427.168080602</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>191198.13859215</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>165209.060241074</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>184708.86053167</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>190823.109693143</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>220423.36989849</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>187123.098683993</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>178469.71230119</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>190935.52810907</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>224118.838499696</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>204572.00046766</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3969.417</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>3873.845</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3222.575</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3830.498</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>3813.4</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3231.886</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3299.407</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3445.947</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>3286.954</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>4053.552</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>3249.612</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>3312.649</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>3379.39</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>4278.936</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>3268.448</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>4158.229</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>3261.063</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>4224.765</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>4229.12</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>3976.799</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>3922.247</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>4129.978</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>4149.127</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>3944.067</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>3753.519</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>3874.107</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3986.103</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>148936.732161773</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>148511.01320058</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>159126.445473367</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>166030.112547981</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>162368.534724205</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>170695.004703828</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>186364.326669966</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>193570.735212041</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>196163.805797197</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>188511.547257937</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>194375.341431725</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>204760.701772362</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>210490.404530534</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>223620.603102401</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>246195.314933028</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>265650.350460009</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>285640.590203818</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>317476.324548933</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>319814.567204229</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>301196.272676591</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>349094.077875866</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>359882.20203635</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>373707.431473059</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>321416.689848154</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>364151.621449716</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>343804.899921721</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>389631.942625551</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>7337.451</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>4265.454</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>4261.731</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4689.845</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>4151.596</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>4489.029</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>4595.85</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>4297.048</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>4106.006</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>4956.695</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>5015.663</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>4506.288</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>3991.393</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>4796.307</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>4686.881</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>5658.469</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>4919.423</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>6810.889</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>7820.11</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>5294.42</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>5329.165</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>6196.492</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>5907.91</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>5049.041</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>5300.698</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>4695.279</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>5962.826</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-6.27</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-8.56</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-6.36</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>8.07</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-12.04</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-14.79</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-2.27</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-12.95</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-2.38</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>10.73</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-3.77</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-4.78</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-5.21</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-17.7</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-27.66</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>30.54</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>23.82</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>22.17</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>37.38</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>25.83</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>49.78</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>14.37</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7.616</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>5.247</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>4.977</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>5.434</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>5.101</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>5.108</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5.126</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>5.278</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>4.946</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>5.204</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>4.607</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4.464</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.519</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>4.914</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4.111</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>3.273</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>3.137</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3.121</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>3.304</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>34973798.414</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2.559</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2.556</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>2.919</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2.412</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2.564</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2.977</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>123628.377743098</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>122193.697909705</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>104526.630031716</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>110647.727619661</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>122607.459992883</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>136729.537896507</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>140114.934677171</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>137946.716365589</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>130172.954838655</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>140214.32793384</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>145744.724675152</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>151065.226102841</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>150002.226687384</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>167962.415574884</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>159677.605874901</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>199123.034296043</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>231365.913209209</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>221347.333826485</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>223979.128328765</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>245743.457008328</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>282196.823337076</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>275622.734954395</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>240968.843950201</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>293603.771422564</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>274021.719386875</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>320369.04859747</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>273960.578782155</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6877290477.36579</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4443880000.00092</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3897107000.00013</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4391743000.00176</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4486603999.99959</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3948424000.0013</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3916299000.0012</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4250936999.9988</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4160642999.99989</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4844361000.00255</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4366133999.99865</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4398987999.99968</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4548186999.99935</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5310759000.00042</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4509973999.99895</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>5388134000.00017</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>4662975999.99994</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5605617000.0002</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5657323000.00041</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>6911529368.1116</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>6598580984.93676</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>7256343611.85452</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>7217555482.96597</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>6936542335.02984</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>6669712619.62948</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>7032484578.40226</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>6819905205.47726</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>8461803744.45548</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>7119702000.00133</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6442480000.00135</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>7080755000.00196</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>7146633999.9991</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6600072000.00114</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6613248999.99974</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6974769999.99841</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6825582999.99983</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>7692919000.00216</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6926699999.99987</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6948990000.00082</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>7086694999.9995</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>7973343000.00024</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6846694999.99923</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>7817463999.9998</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>7042354000.001</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8100009000.0004</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8186731000.00063</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>8228331068.08972</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>7895483732.50425</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>8702257461.97285</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>8681695129.21632</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>8363093521.65983</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>8070182770.72785</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>8544562558.98054</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>8302296393.77659</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3969417033.96925</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3873844810.18103</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3222575026.43786</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3830497502.61591</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3813399852.46872</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3231886289.89403</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3299407378.05097</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3445947246.06913</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3286953735.62447</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4053551507.67566</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3249611901.7969</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3312648947.16651</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3379389963.47423</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4278935923.76262</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3268448244.76859</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4158229449.9808</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3261062547.89657</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4224765023.85764</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4229120337.40019</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3976798802.46333</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>3922246556.20656</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>4129977949.01936</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>4149127325.37505</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>3944066649.16846</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>3753519366.90519</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>3874106696.08614</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3986103200.33349</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4371382.43163532</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3675099.99999876</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3272399.99999889</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3638899.99999968</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3676899.99999919</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3309900.00000032</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3302399.99999875</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3475099.99999956</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3464200.00000002</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3937699.99999896</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3458599.99999917</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3466700.00000005</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>3527800.00000076</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4079599.99999953</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3414100.00000034</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4030799.99999948</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3550399.99999961</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4171700.00000046</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>4239000.00000075</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>4265337.02471793</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>4100857.95687958</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>4527609.40538153</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>4517146.45372896</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>4331756.26377686</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>4184732.12345744</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>4428320.14651819</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>4310577.90265604</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3609213.69709116</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3059299.99999927</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2714299.99999877</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3016099.99999975</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3066199.99999925</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2743200.00000028</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2732674.99999867</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2895049.99999947</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2890725.00000002</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3280999.99999882</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2911199.99999927</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2928800.00000008</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2982000.00000068</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3456299.9999995</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2917500.00000029</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3473799.99999948</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3033199.99999971</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>3588800.00000046</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>3640900.00000084</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>3644130.19286549</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>3489446.401301</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3841927.42770372</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>3820585.57969366</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>3652716.90618879</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>3517351.58405624</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>3705314.51833295</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3598494.18045673</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8461803744.45548</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>7119702000.00133</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6442480000.00135</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>7080755000.00196</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>7146633999.9991</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6600072000.00114</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6613248999.99974</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6974769999.99841</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6825582999.99983</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>7692919000.00216</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6926699999.99987</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6948990000.00082</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>7086694999.9995</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>7973343000.00024</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6846694999.99923</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>7817463999.9998</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>7042354000.001</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8100009000.0004</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8186731000.00063</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>8228331068.08972</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>7895483732.50425</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>8702257461.97285</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>8681695129.21632</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>8363093521.65983</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>8070182770.72785</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>8544562558.98054</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>8302296393.77659</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6877290477.36579</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4443880000.00092</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3897107000.00013</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4391743000.00176</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4486603999.99959</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3948424000.0013</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3916299000.0012</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4250936999.9988</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4160642999.99989</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4844361000.00255</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4366133999.99865</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4398987999.99968</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4548186999.99935</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5310759000.00042</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4509973999.99895</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>5388134000.00017</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>4662975999.99994</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5605617000.0002</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5657323000.00041</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>6911529368.1116</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>6598580984.93676</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>7256343611.85452</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>7217555482.96597</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>6936542335.02984</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>6669712619.62948</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>7032484578.40226</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>6819905205.47726</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>546287.975952012</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>553541.852892575</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>550686.948004601</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>572930.971199544</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>593734.428404173</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>645670.132164362</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>684272.970438466</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>702165.787526999</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>678465.972337924</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>698749.564889556</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>734442.356782329</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>769061.577284861</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>778653.839042377</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>854329.310433851</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>875592.198282184</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1004799.81284272</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1142785.48383654</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1187525.91593113</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1202608.81832039</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1219252.48233405</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1405199.77454396</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1406287.00661254</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1398105.59403686</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1398259.22479329</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1436036.03167057</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1461925.00732569</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1512243.98098754</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>175229.528248466</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>174628.904151646</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>183548.083049689</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>189391.260094869</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>187442.190798599</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>198649.830319394</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>214882.097353427</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>225145.168315859</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>225111.3440502</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>220662.163760339</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>228436.784181492</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>240171.113557342</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>248627.712678455</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>261251.31497385</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>283295.312588047</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>304725.81084237</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>342798.77560853</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>374938.453773098</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>370067.651813713</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>366162.817231899</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>418317.907706488</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>419988.922253517</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>449302.102266205</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>396123.772409094</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>449183.104600414</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>411948.156769813</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>470220.167807605</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
